--- a/LDC.xlsx
+++ b/LDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy-GGP-PNG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60E684BF-AA5E-4FA2-8C50-94899DA00B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{60E684BF-AA5E-4FA2-8C50-94899DA00B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E719A606-49CB-45F7-9F99-0A633B73A4AC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{872C3CD0-F166-47E8-A8A7-3CF35D3DE171}"/>
   </bookViews>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045F0D33-860E-441B-A2B8-0B0FA6A6F9B0}">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -524,7 +524,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -647,19 +647,19 @@
         <v>0</v>
       </c>
       <c r="F5">
+        <v>0.2</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>0.1</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -729,19 +729,19 @@
         <v>0</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>0.1</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -770,19 +770,19 @@
         <v>0</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>0.1</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -808,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -919,10 +919,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -966,13 +966,13 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1013,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="B16">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -1396,6 +1396,9 @@
       <c r="I23">
         <v>0</v>
       </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
       <c r="K23">
         <v>0</v>
       </c>
@@ -1859,22 +1862,22 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1883,306 +1886,19 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>0</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>0</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>0</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>0</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>0</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>0</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42">
         <v>1</v>
-      </c>
-      <c r="B42">
-        <v>0.6</v>
-      </c>
-      <c r="C42">
-        <v>0.95</v>
-      </c>
-      <c r="D42">
-        <v>0.95</v>
-      </c>
-      <c r="E42">
-        <v>0.7</v>
-      </c>
-      <c r="F42">
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
-      <c r="I42">
-        <v>0.9</v>
-      </c>
-      <c r="J42">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
-      <c r="L42">
-        <v>0.8</v>
-      </c>
-      <c r="M42">
-        <v>0.9</v>
       </c>
     </row>
   </sheetData>
